--- a/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>GMER</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
-        <v>100</v>
-      </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -844,13 +848,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -873,13 +877,16 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -894,7 +901,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -956,14 +963,17 @@
       <c r="AC9" s="3">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>4</v>
+      <c r="AD9" s="3">
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -983,19 +993,19 @@
         <v>-100</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
@@ -1022,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
         <v>0</v>
@@ -1045,14 +1055,17 @@
       <c r="AC10" s="3">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>4</v>
+      <c r="AD10" s="3">
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1280,13 +1300,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1321,20 +1341,20 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1399,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3">
         <v>100</v>
@@ -1411,11 +1434,11 @@
         <v>100</v>
       </c>
       <c r="V15" s="3">
+        <v>100</v>
+      </c>
+      <c r="W15" s="3">
         <v>300</v>
       </c>
-      <c r="W15" s="3">
-        <v>100</v>
-      </c>
       <c r="X15" s="3">
         <v>100</v>
       </c>
@@ -1435,13 +1458,16 @@
         <v>100</v>
       </c>
       <c r="AD15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="3">
         <v>200</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,32 +1506,32 @@
         <v>300</v>
       </c>
       <c r="E17" s="3">
+        <v>300</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>500</v>
       </c>
       <c r="G17" s="3">
         <v>500</v>
       </c>
       <c r="H17" s="3">
+        <v>500</v>
+      </c>
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>100</v>
-      </c>
       <c r="N17" s="3">
         <v>100</v>
       </c>
@@ -1518,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="R17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>200</v>
@@ -1527,22 +1554,22 @@
         <v>200</v>
       </c>
       <c r="U17" s="3">
+        <v>200</v>
+      </c>
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>200</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>300</v>
       </c>
       <c r="AA17" s="3">
         <v>300</v>
@@ -1554,13 +1581,16 @@
         <v>300</v>
       </c>
       <c r="AD17" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,28 +1598,28 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-500</v>
       </c>
       <c r="G18" s="3">
         <v>-500</v>
       </c>
       <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-100</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
@@ -1607,7 +1637,7 @@
         <v>-100</v>
       </c>
       <c r="R18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="S18" s="3">
         <v>-200</v>
@@ -1616,22 +1646,22 @@
         <v>-200</v>
       </c>
       <c r="U18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-300</v>
       </c>
       <c r="AA18" s="3">
         <v>-300</v>
@@ -1643,13 +1673,16 @@
         <v>-300</v>
       </c>
       <c r="AD18" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1705,73 +1739,76 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>16600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>100</v>
-      </c>
       <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,88 +1816,91 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F21" s="3">
         <v>-400</v>
       </c>
       <c r="G21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
-        <v>100</v>
-      </c>
       <c r="N21" s="3">
+        <v>100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
-        <v>100</v>
-      </c>
       <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-200</v>
       </c>
       <c r="S21" s="3">
         <v>-200</v>
       </c>
       <c r="T21" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="U21" s="3">
         <v>-100</v>
       </c>
       <c r="V21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
-        <v>100</v>
-      </c>
       <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
-        <v>100</v>
-      </c>
       <c r="AB21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1930,11 +1970,11 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1943,13 +1983,16 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1957,88 +2000,91 @@
         <v>-300</v>
       </c>
       <c r="E23" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F23" s="3">
         <v>-400</v>
       </c>
       <c r="G23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
-        <v>100</v>
-      </c>
       <c r="N23" s="3">
+        <v>100</v>
+      </c>
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
-        <v>100</v>
-      </c>
       <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2264,11 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2224,88 +2276,91 @@
         <v>-300</v>
       </c>
       <c r="E26" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F26" s="3">
         <v>-400</v>
       </c>
       <c r="G26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
-        <v>100</v>
-      </c>
       <c r="N26" s="3">
+        <v>100</v>
+      </c>
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
-        <v>100</v>
-      </c>
       <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2313,88 +2368,91 @@
         <v>-300</v>
       </c>
       <c r="E27" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F27" s="3">
         <v>-400</v>
       </c>
       <c r="G27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
-        <v>100</v>
-      </c>
       <c r="N27" s="3">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
-        <v>100</v>
-      </c>
       <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2773,73 +2843,76 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-16600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>100</v>
-      </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2847,88 +2920,91 @@
         <v>-300</v>
       </c>
       <c r="E33" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F33" s="3">
         <v>-400</v>
       </c>
       <c r="G33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
-        <v>100</v>
-      </c>
       <c r="N33" s="3">
+        <v>100</v>
+      </c>
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
-        <v>100</v>
-      </c>
       <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3092,11 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3025,182 +3104,188 @@
         <v>-300</v>
       </c>
       <c r="E35" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F35" s="3">
         <v>-400</v>
       </c>
       <c r="G35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
-        <v>100</v>
-      </c>
       <c r="N35" s="3">
+        <v>100</v>
+      </c>
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
-        <v>100</v>
-      </c>
       <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,35 +3351,36 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
         <v>0</v>
       </c>
@@ -3334,28 +3421,31 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="3">
         <v>100</v>
       </c>
       <c r="AA41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="3">
         <v>100</v>
       </c>
       <c r="AD41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,16 +3533,19 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
@@ -3469,8 +3562,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3530,10 +3623,13 @@
         <v>0</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3692,53 +3791,56 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>0</v>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3779,16 +3881,16 @@
         <v>0</v>
       </c>
       <c r="Y46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3">
         <v>100</v>
       </c>
       <c r="AA46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3810,8 +3915,8 @@
       <c r="E47" s="3">
         <v>0</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
@@ -3825,8 +3930,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3951,17 +4059,17 @@
         <v>0</v>
       </c>
       <c r="W48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X48" s="3">
         <v>100</v>
       </c>
       <c r="Y48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
-      </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3998,7 +4109,7 @@
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>300</v>
@@ -4007,16 +4118,16 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
-        <v>100</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="M49" s="3">
+        <v>100</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
@@ -4024,50 +4135,53 @@
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T49" s="3">
+        <v>100</v>
+      </c>
+      <c r="U49" s="3">
         <v>200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>500</v>
-      </c>
-      <c r="W49" s="3">
-        <v>600</v>
       </c>
       <c r="X49" s="3">
         <v>600</v>
       </c>
       <c r="Y49" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z49" s="3">
         <v>700</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>800</v>
       </c>
       <c r="AA49" s="3">
         <v>800</v>
       </c>
       <c r="AB49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AC49" s="3">
         <v>900</v>
       </c>
       <c r="AD49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE49" s="3">
         <v>1000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4303,14 +4423,14 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
@@ -4327,14 +4447,17 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4431,31 +4557,31 @@
         <v>400</v>
       </c>
       <c r="E54" s="3">
+        <v>400</v>
+      </c>
+      <c r="F54" s="3">
         <v>700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3">
-        <v>100</v>
-      </c>
       <c r="M54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N54" s="3">
         <v>0</v>
@@ -4473,46 +4599,49 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T54" s="3">
+        <v>100</v>
+      </c>
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>900</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>800</v>
       </c>
       <c r="AA54" s="3">
         <v>800</v>
       </c>
       <c r="AB54" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AC54" s="3">
         <v>1000</v>
       </c>
       <c r="AD54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE54" s="3">
         <v>1100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,13 +4707,14 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
@@ -4598,7 +4729,7 @@
         <v>400</v>
       </c>
       <c r="I57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J57" s="3">
         <v>300</v>
@@ -4607,7 +4738,7 @@
         <v>300</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -4619,7 +4750,7 @@
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -4640,11 +4771,11 @@
         <v>100</v>
       </c>
       <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
-        <v>100</v>
-      </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
@@ -4666,8 +4797,11 @@
       <c r="AE57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4693,70 +4827,73 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2300</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2200</v>
       </c>
       <c r="O58" s="3">
         <v>2200</v>
       </c>
       <c r="P58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1900</v>
       </c>
       <c r="R58" s="3">
         <v>1900</v>
       </c>
       <c r="S58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T58" s="3">
         <v>1800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>500</v>
       </c>
-      <c r="AD58" s="3">
-        <v>100</v>
-      </c>
       <c r="AE58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4782,75 +4919,78 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>16500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>500</v>
       </c>
       <c r="U59" s="3">
         <v>500</v>
       </c>
       <c r="V59" s="3">
+        <v>500</v>
+      </c>
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
-      </c>
-      <c r="X59" s="3">
-        <v>400</v>
       </c>
       <c r="Y59" s="3">
         <v>400</v>
       </c>
       <c r="Z59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>200</v>
       </c>
       <c r="AD59" s="3">
         <v>200</v>
       </c>
       <c r="AE59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
         <v>400</v>
@@ -4865,76 +5005,79 @@
         <v>400</v>
       </c>
       <c r="I60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J60" s="3">
         <v>300</v>
       </c>
       <c r="K60" s="3">
+        <v>300</v>
+      </c>
+      <c r="L60" s="3">
         <v>19500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>2800</v>
       </c>
       <c r="R60" s="3">
         <v>2800</v>
       </c>
       <c r="S60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T60" s="3">
         <v>2500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5017,13 +5160,16 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5033,14 +5179,14 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -5057,8 +5203,8 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,13 +5533,16 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
         <v>400</v>
@@ -5399,76 +5557,79 @@
         <v>400</v>
       </c>
       <c r="I66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J66" s="3">
         <v>300</v>
       </c>
       <c r="K66" s="3">
+        <v>300</v>
+      </c>
+      <c r="L66" s="3">
         <v>19500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>2800</v>
       </c>
       <c r="R66" s="3">
         <v>2800</v>
       </c>
       <c r="S66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5759,16 +5927,19 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>200</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-23600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-7600</v>
       </c>
       <c r="P72" s="3">
         <v>-7600</v>
       </c>
       <c r="Q72" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R72" s="3">
         <v>-7100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-4900</v>
       </c>
       <c r="Z72" s="3">
         <v>-4900</v>
       </c>
       <c r="AA72" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="E76" s="3">
+        <v>100</v>
+      </c>
+      <c r="F76" s="3">
         <v>300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-19100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-6900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-3600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-2800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-2700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-2400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-400</v>
       </c>
-      <c r="AC76" s="3">
-        <v>100</v>
-      </c>
       <c r="AD76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE76" s="3">
         <v>400</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6579,108 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6493,88 +6688,91 @@
         <v>-300</v>
       </c>
       <c r="E81" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F81" s="3">
         <v>-400</v>
       </c>
       <c r="G81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
-        <v>100</v>
-      </c>
       <c r="N81" s="3">
+        <v>100</v>
+      </c>
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
-        <v>100</v>
-      </c>
       <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6654,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -6666,11 +6865,11 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
+        <v>100</v>
+      </c>
+      <c r="W83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3">
-        <v>100</v>
-      </c>
       <c r="X83" s="3">
         <v>100</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,13 +7354,16 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>-300</v>
@@ -7158,19 +7375,19 @@
         <v>-300</v>
       </c>
       <c r="H89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-500</v>
       </c>
       <c r="J89" s="3">
         <v>-500</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="L89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
         <v>-100</v>
@@ -7200,19 +7417,19 @@
         <v>-100</v>
       </c>
       <c r="V89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-200</v>
       </c>
       <c r="AA89" s="3">
         <v>-200</v>
@@ -7224,13 +7441,16 @@
         <v>-200</v>
       </c>
       <c r="AD89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7286,14 +7507,14 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7315,14 +7536,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7336,8 +7557,8 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
@@ -7345,14 +7566,17 @@
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7553,17 +7783,17 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -7606,20 +7836,23 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8031,14 +8277,14 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
-        <v>100</v>
-      </c>
       <c r="M100" s="3">
         <v>100</v>
       </c>
@@ -8067,37 +8313,40 @@
         <v>100</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
       <c r="X100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="3">
         <v>200</v>
       </c>
       <c r="Z100" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
       <c r="AB100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
         <v>200</v>
       </c>
       <c r="AD100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,13 +8434,16 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>-300</v>
@@ -8203,17 +8455,17 @@
         <v>-300</v>
       </c>
       <c r="H102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -8251,20 +8503,20 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>GMER</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -818,16 +825,16 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -851,16 +858,16 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -880,19 +887,25 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -904,10 +917,10 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -966,14 +979,20 @@
       <c r="AD9" s="3">
         <v>0</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -981,10 +1000,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>-100</v>
@@ -996,22 +1015,22 @@
         <v>-100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>0</v>
@@ -1035,16 +1054,16 @@
         <v>0</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1058,14 +1077,20 @@
       <c r="AD10" s="3">
         <v>0</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,13 +1315,19 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1303,16 +1342,16 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
@@ -1344,23 +1383,23 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1425,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3">
         <v>100</v>
@@ -1437,14 +1482,14 @@
         <v>100</v>
       </c>
       <c r="W15" s="3">
+        <v>100</v>
+      </c>
+      <c r="X15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y15" s="3">
         <v>300</v>
       </c>
-      <c r="X15" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>100</v>
-      </c>
       <c r="Z15" s="3">
         <v>100</v>
       </c>
@@ -1461,13 +1506,19 @@
         <v>100</v>
       </c>
       <c r="AE15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,47 +1548,49 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>700</v>
       </c>
       <c r="J17" s="3">
         <v>500</v>
       </c>
       <c r="K17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L17" s="3">
         <v>500</v>
       </c>
       <c r="M17" s="3">
+        <v>600</v>
+      </c>
+      <c r="N17" s="3">
+        <v>500</v>
+      </c>
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>100</v>
-      </c>
-      <c r="O17" s="3">
-        <v>100</v>
-      </c>
       <c r="P17" s="3">
         <v>100</v>
       </c>
@@ -1548,25 +1601,25 @@
         <v>100</v>
       </c>
       <c r="S17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U17" s="3">
         <v>200</v>
       </c>
       <c r="V17" s="3">
+        <v>200</v>
+      </c>
+      <c r="W17" s="3">
+        <v>200</v>
+      </c>
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>300</v>
       </c>
       <c r="Z17" s="3">
         <v>200</v>
@@ -1575,7 +1628,7 @@
         <v>300</v>
       </c>
       <c r="AB17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC17" s="3">
         <v>300</v>
@@ -1584,13 +1637,19 @@
         <v>300</v>
       </c>
       <c r="AE17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG17" s="3">
         <v>200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,34 +1657,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-700</v>
       </c>
       <c r="J18" s="3">
         <v>-500</v>
       </c>
       <c r="K18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
@@ -1640,34 +1699,34 @@
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U18" s="3">
         <v>-200</v>
       </c>
       <c r="V18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-200</v>
       </c>
       <c r="AA18" s="3">
         <v>-300</v>
       </c>
       <c r="AB18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AC18" s="3">
         <v>-300</v>
@@ -1676,13 +1735,19 @@
         <v>-300</v>
       </c>
       <c r="AE18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,7 +1791,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1742,73 +1809,79 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>16600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-12100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-300</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>300</v>
-      </c>
       <c r="AA20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>300</v>
       </c>
       <c r="AC20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,99 +1889,105 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-700</v>
       </c>
       <c r="J21" s="3">
         <v>-500</v>
       </c>
       <c r="K21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M21" s="3">
         <v>16000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-12300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3400</v>
       </c>
-      <c r="N21" s="3">
-        <v>100</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AB21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>400</v>
       </c>
       <c r="AF21" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1973,100 +2052,106 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-700</v>
       </c>
       <c r="J23" s="3">
         <v>-500</v>
       </c>
       <c r="K23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M23" s="3">
         <v>16000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-12300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
-        <v>100</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-400</v>
       </c>
       <c r="U23" s="3">
         <v>-300</v>
       </c>
       <c r="V23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-600</v>
       </c>
       <c r="AB23" s="3">
         <v>0</v>
@@ -2075,16 +2160,22 @@
         <v>-600</v>
       </c>
       <c r="AD23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF23" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,82 +2364,88 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-700</v>
       </c>
       <c r="J26" s="3">
         <v>-500</v>
       </c>
       <c r="K26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M26" s="3">
         <v>16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-12300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
-        <v>100</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-400</v>
       </c>
       <c r="U26" s="3">
         <v>-300</v>
       </c>
       <c r="V26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-600</v>
       </c>
       <c r="AB26" s="3">
         <v>0</v>
@@ -2351,90 +2454,96 @@
         <v>-600</v>
       </c>
       <c r="AD26" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF26" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-700</v>
       </c>
       <c r="J27" s="3">
         <v>-500</v>
       </c>
       <c r="K27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M27" s="3">
         <v>16000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-12300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
-        <v>100</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
+        <v>100</v>
+      </c>
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-400</v>
       </c>
       <c r="U27" s="3">
         <v>-300</v>
       </c>
       <c r="V27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-600</v>
       </c>
       <c r="AB27" s="3">
         <v>0</v>
@@ -2443,16 +2552,22 @@
         <v>-600</v>
       </c>
       <c r="AD27" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF27" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,7 +2967,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2846,147 +2985,153 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-16600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>12100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>300</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>300</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
-      </c>
       <c r="T32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>100</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-300</v>
-      </c>
       <c r="AA32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-300</v>
       </c>
       <c r="AC32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-700</v>
       </c>
       <c r="J33" s="3">
         <v>-500</v>
       </c>
       <c r="K33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M33" s="3">
         <v>16000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-12300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
-        <v>100</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
+        <v>100</v>
+      </c>
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-400</v>
       </c>
       <c r="U33" s="3">
         <v>-300</v>
       </c>
       <c r="V33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-600</v>
       </c>
       <c r="AB33" s="3">
         <v>0</v>
@@ -2995,16 +3140,22 @@
         <v>-600</v>
       </c>
       <c r="AD33" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF33" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,82 +3246,88 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-700</v>
       </c>
       <c r="J35" s="3">
         <v>-500</v>
       </c>
       <c r="K35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M35" s="3">
         <v>16000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-12300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
-        <v>100</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
+        <v>100</v>
+      </c>
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-400</v>
       </c>
       <c r="U35" s="3">
         <v>-300</v>
       </c>
       <c r="V35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-600</v>
       </c>
       <c r="AB35" s="3">
         <v>0</v>
@@ -3179,113 +3336,125 @@
         <v>-600</v>
       </c>
       <c r="AD35" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF35" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3523,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3364,29 +3537,29 @@
         <v>300</v>
       </c>
       <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>300</v>
+      </c>
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2400</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
@@ -3424,28 +3597,34 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
         <v>100</v>
       </c>
       <c r="AD41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,22 +3715,28 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
@@ -3565,11 +3750,11 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3626,10 +3811,16 @@
         <v>0</v>
       </c>
       <c r="AF43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,16 +3911,22 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3794,17 +3991,17 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
+      <c r="AA45" s="3">
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -3812,8 +4009,14 @@
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3821,32 +4024,32 @@
         <v>200</v>
       </c>
       <c r="E46" s="3">
+        <v>400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>200</v>
+      </c>
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3884,19 +4087,19 @@
         <v>0</v>
       </c>
       <c r="Z46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
       </c>
       <c r="AD46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="3">
         <v>100</v>
@@ -3904,8 +4107,14 @@
       <c r="AF46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3918,11 +4127,11 @@
       <c r="F47" s="3">
         <v>0</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
@@ -3933,11 +4142,11 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3996,13 +4205,19 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -4062,20 +4277,20 @@
         <v>0</v>
       </c>
       <c r="X48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3">
         <v>200</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>0</v>
-      </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4112,76 +4333,82 @@
         <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
         <v>300</v>
       </c>
       <c r="M49" s="3">
-        <v>100</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
+        <v>300</v>
       </c>
       <c r="O49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>100</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>100</v>
+      </c>
+      <c r="W49" s="3">
         <v>200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4426,8 +4665,8 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4435,8 +4674,8 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
+      <c r="Z52" s="3">
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
@@ -4450,14 +4689,20 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,46 +4793,52 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>500</v>
+      </c>
+      <c r="F54" s="3">
         <v>400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>300</v>
       </c>
-      <c r="M54" s="3">
-        <v>100</v>
-      </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
       <c r="O54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -4602,46 +4853,52 @@
         <v>0</v>
       </c>
       <c r="T54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U54" s="3">
+        <v>0</v>
+      </c>
+      <c r="V54" s="3">
+        <v>100</v>
+      </c>
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>700</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>800</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>900</v>
       </c>
       <c r="AA54" s="3">
         <v>800</v>
       </c>
       <c r="AB54" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC54" s="3">
         <v>800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE54" s="3">
         <v>1000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,19 +4967,21 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
-        <v>400</v>
-      </c>
       <c r="F57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
@@ -4732,19 +4993,19 @@
         <v>400</v>
       </c>
       <c r="J57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>300</v>
       </c>
       <c r="M57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -4753,10 +5014,10 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -4774,14 +5035,14 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>100</v>
-      </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4830,70 +5097,76 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>900</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1000</v>
       </c>
       <c r="AB58" s="3">
         <v>900</v>
       </c>
       <c r="AC58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>500</v>
       </c>
-      <c r="AE58" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4922,81 +5195,87 @@
         <v>0</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>16500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>800</v>
       </c>
       <c r="T59" s="3">
         <v>700</v>
       </c>
       <c r="U59" s="3">
+        <v>800</v>
+      </c>
+      <c r="V59" s="3">
+        <v>700</v>
+      </c>
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>500</v>
       </c>
       <c r="AD59" s="3">
         <v>200</v>
       </c>
       <c r="AE59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF59" s="3">
         <v>200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
-        <v>400</v>
-      </c>
       <c r="F60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G60" s="3">
         <v>400</v>
@@ -5008,76 +5287,82 @@
         <v>400</v>
       </c>
       <c r="J60" s="3">
+        <v>400</v>
+      </c>
+      <c r="K60" s="3">
+        <v>400</v>
+      </c>
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5163,13 +5448,19 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5182,17 +5473,17 @@
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -5206,11 +5497,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,19 +5845,25 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
       </c>
-      <c r="E66" s="3">
-        <v>400</v>
-      </c>
       <c r="F66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G66" s="3">
         <v>400</v>
@@ -5560,76 +5875,82 @@
         <v>400</v>
       </c>
       <c r="J66" s="3">
+        <v>400</v>
+      </c>
+      <c r="K66" s="3">
+        <v>400</v>
+      </c>
+      <c r="L66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>19500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5930,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-10700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-10500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-9700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-9300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-8800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-7600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-23600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-11300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-7800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-8000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-7100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-6700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-6300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-6100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-5900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-4300</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-3500</v>
       </c>
       <c r="AF72" s="3">
         <v>-3700</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>-3700</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3">
         <v>-200</v>
       </c>
-      <c r="E76" s="3">
-        <v>100</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>100</v>
+      </c>
+      <c r="H76" s="3">
         <v>300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-19100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-6900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-3500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-3600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-3400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-2800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-2700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-2400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-2100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-1800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-1600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-400</v>
       </c>
-      <c r="AD76" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG76" s="3">
         <v>400</v>
       </c>
-      <c r="AF76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,179 +6959,191 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-700</v>
       </c>
       <c r="J81" s="3">
         <v>-500</v>
       </c>
       <c r="K81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M81" s="3">
         <v>16000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-12300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
-        <v>100</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
+        <v>100</v>
+      </c>
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-400</v>
       </c>
       <c r="U81" s="3">
         <v>-300</v>
       </c>
       <c r="V81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-600</v>
       </c>
       <c r="AB81" s="3">
         <v>0</v>
@@ -6763,16 +7152,22 @@
         <v>-600</v>
       </c>
       <c r="AD81" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="AF81" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6856,10 +7253,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6868,14 +7265,14 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
-      </c>
       <c r="Z83" s="3">
         <v>100</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7366,10 +7799,10 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
@@ -7378,22 +7811,22 @@
         <v>-300</v>
       </c>
       <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
-      </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>-100</v>
@@ -7420,22 +7853,22 @@
         <v>-100</v>
       </c>
       <c r="W89" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="X89" s="3">
         <v>-100</v>
       </c>
       <c r="Y89" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="Z89" s="3">
         <v>-100</v>
       </c>
       <c r="AA89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AB89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC89" s="3">
         <v>-200</v>
@@ -7444,13 +7877,19 @@
         <v>-200</v>
       </c>
       <c r="AE89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7510,17 +7951,17 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7539,17 +7980,17 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -7560,23 +8001,29 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7768,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -7786,20 +8245,20 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -7839,20 +8298,26 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8280,17 +8771,17 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>100</v>
-      </c>
       <c r="O100" s="3">
         <v>100</v>
       </c>
@@ -8316,37 +8807,43 @@
         <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8446,10 +8949,10 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-300</v>
@@ -8458,20 +8961,20 @@
         <v>-300</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -8506,27 +9009,33 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>100</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GMER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>GMER</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -831,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -864,13 +868,13 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <v>100</v>
       </c>
       <c r="AA8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,13 +909,13 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -923,7 +930,7 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -985,14 +992,17 @@
       <c r="AF9" s="3">
         <v>0</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>4</v>
+      <c r="AG9" s="3">
+        <v>0</v>
       </c>
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,13 +1010,13 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>-100</v>
@@ -1021,19 +1031,19 @@
         <v>-100</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
@@ -1060,13 +1070,13 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="3">
         <v>0</v>
@@ -1083,14 +1093,17 @@
       <c r="AF10" s="3">
         <v>0</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>4</v>
+      <c r="AG10" s="3">
+        <v>0</v>
       </c>
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,13 +1338,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1348,13 +1368,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -1389,20 +1409,20 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1476,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
         <v>100</v>
@@ -1488,11 +1511,11 @@
         <v>100</v>
       </c>
       <c r="Y15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z15" s="3">
         <v>300</v>
       </c>
-      <c r="Z15" s="3">
-        <v>100</v>
-      </c>
       <c r="AA15" s="3">
         <v>100</v>
       </c>
@@ -1512,13 +1535,16 @@
         <v>100</v>
       </c>
       <c r="AG15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH15" s="3">
         <v>200</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,50 +1576,51 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
       <c r="F17" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3">
         <v>300</v>
       </c>
       <c r="H17" s="3">
+        <v>300</v>
+      </c>
+      <c r="I17" s="3">
         <v>400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>500</v>
       </c>
       <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
       <c r="Q17" s="3">
         <v>100</v>
       </c>
@@ -1607,7 +1634,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V17" s="3">
         <v>200</v>
@@ -1616,22 +1643,22 @@
         <v>200</v>
       </c>
       <c r="X17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>200</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>300</v>
       </c>
       <c r="AD17" s="3">
         <v>300</v>
@@ -1643,13 +1670,16 @@
         <v>300</v>
       </c>
       <c r="AG17" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AH17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,37 +1687,37 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
         <v>-300</v>
       </c>
       <c r="H18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-500</v>
       </c>
       <c r="J18" s="3">
         <v>-500</v>
       </c>
       <c r="K18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-100</v>
       </c>
       <c r="P18" s="3">
         <v>-100</v>
@@ -1705,7 +1735,7 @@
         <v>-100</v>
       </c>
       <c r="U18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
@@ -1714,22 +1744,22 @@
         <v>-200</v>
       </c>
       <c r="X18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-300</v>
       </c>
       <c r="AD18" s="3">
         <v>-300</v>
@@ -1741,13 +1771,16 @@
         <v>-300</v>
       </c>
       <c r="AG18" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AH18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,10 +1825,10 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1815,73 +1849,76 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>16600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
-        <v>100</v>
-      </c>
       <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1889,97 +1926,100 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3">
         <v>-300</v>
       </c>
       <c r="H21" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I21" s="3">
         <v>-400</v>
       </c>
       <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
       <c r="Q21" s="3">
+        <v>100</v>
+      </c>
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
-        <v>100</v>
-      </c>
       <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-200</v>
       </c>
       <c r="V21" s="3">
         <v>-200</v>
       </c>
       <c r="W21" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X21" s="3">
         <v>-100</v>
       </c>
       <c r="Y21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
-        <v>100</v>
-      </c>
       <c r="AC21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3">
-        <v>100</v>
-      </c>
       <c r="AE21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1989,8 +2029,8 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -2058,11 +2098,11 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2071,111 +2111,117 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
-        <v>100</v>
-      </c>
       <c r="F23" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G23" s="3">
         <v>-300</v>
       </c>
       <c r="H23" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I23" s="3">
         <v>-400</v>
       </c>
       <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
-        <v>100</v>
-      </c>
       <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
-        <v>100</v>
-      </c>
       <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
       <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
-        <v>100</v>
-      </c>
       <c r="F26" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
         <v>-300</v>
       </c>
       <c r="H26" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I26" s="3">
         <v>-400</v>
       </c>
       <c r="J26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
-        <v>100</v>
-      </c>
       <c r="Q26" s="3">
+        <v>100</v>
+      </c>
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
-        <v>100</v>
-      </c>
       <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
-        <v>100</v>
-      </c>
       <c r="F27" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
         <v>-300</v>
       </c>
       <c r="H27" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I27" s="3">
         <v>-400</v>
       </c>
       <c r="J27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
-        <v>100</v>
-      </c>
       <c r="Q27" s="3">
+        <v>100</v>
+      </c>
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
-        <v>100</v>
-      </c>
       <c r="S27" s="3">
+        <v>100</v>
+      </c>
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,11 +3037,11 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2991,171 +3061,177 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-16600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>100</v>
-      </c>
       <c r="Z32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
-        <v>100</v>
-      </c>
       <c r="F33" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
         <v>-300</v>
       </c>
       <c r="H33" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I33" s="3">
         <v>-400</v>
       </c>
       <c r="J33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
-        <v>100</v>
-      </c>
       <c r="Q33" s="3">
+        <v>100</v>
+      </c>
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
-        <v>100</v>
-      </c>
       <c r="S33" s="3">
+        <v>100</v>
+      </c>
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-300</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
-        <v>100</v>
-      </c>
       <c r="F35" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
         <v>-300</v>
       </c>
       <c r="H35" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I35" s="3">
         <v>-400</v>
       </c>
       <c r="J35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
-        <v>100</v>
-      </c>
       <c r="Q35" s="3">
+        <v>100</v>
+      </c>
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
-        <v>100</v>
-      </c>
       <c r="S35" s="3">
+        <v>100</v>
+      </c>
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-300</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,44 +3611,45 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
@@ -3603,28 +3690,31 @@
         <v>0</v>
       </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="3">
         <v>100</v>
       </c>
       <c r="AD41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
         <v>100</v>
       </c>
       <c r="AG41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,25 +3811,28 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
@@ -3756,8 +3849,8 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3817,10 +3910,13 @@
         <v>0</v>
       </c>
       <c r="AH43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,19 +4013,22 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3997,62 +4096,65 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
@@ -4093,16 +4195,16 @@
         <v>0</v>
       </c>
       <c r="AB46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
       </c>
       <c r="AD46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="3">
         <v>100</v>
@@ -4113,13 +4215,16 @@
       <c r="AH46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -4133,8 +4238,8 @@
       <c r="H47" s="3">
         <v>0</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
+      <c r="I47" s="3">
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
@@ -4148,8 +4253,8 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4211,16 +4316,19 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
@@ -4283,17 +4391,17 @@
         <v>0</v>
       </c>
       <c r="Z48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="3">
         <v>100</v>
       </c>
       <c r="AB48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
-      </c>
       <c r="AD48" s="3">
         <v>0</v>
       </c>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4339,7 +4450,7 @@
         <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M49" s="3">
         <v>300</v>
@@ -4348,16 +4459,16 @@
         <v>300</v>
       </c>
       <c r="O49" s="3">
-        <v>100</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="P49" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
@@ -4365,50 +4476,53 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W49" s="3">
+        <v>100</v>
+      </c>
+      <c r="X49" s="3">
         <v>200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>500</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>600</v>
       </c>
       <c r="AA49" s="3">
         <v>600</v>
       </c>
       <c r="AB49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC49" s="3">
         <v>700</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>800</v>
       </c>
       <c r="AD49" s="3">
         <v>800</v>
       </c>
       <c r="AE49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AF49" s="3">
         <v>900</v>
       </c>
       <c r="AG49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH49" s="3">
         <v>1000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4671,14 +4791,14 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
@@ -4695,14 +4815,17 @@
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,49 +4922,52 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200</v>
+      </c>
+      <c r="E54" s="3">
         <v>300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>500</v>
-      </c>
-      <c r="F54" s="3">
-        <v>400</v>
       </c>
       <c r="G54" s="3">
         <v>400</v>
       </c>
       <c r="H54" s="3">
+        <v>400</v>
+      </c>
+      <c r="I54" s="3">
         <v>700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>300</v>
       </c>
-      <c r="O54" s="3">
-        <v>100</v>
-      </c>
       <c r="P54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="3">
         <v>0</v>
@@ -4859,46 +4985,49 @@
         <v>0</v>
       </c>
       <c r="V54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W54" s="3">
+        <v>100</v>
+      </c>
+      <c r="X54" s="3">
         <v>200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>900</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>800</v>
       </c>
       <c r="AD54" s="3">
         <v>800</v>
       </c>
       <c r="AE54" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AF54" s="3">
         <v>1000</v>
       </c>
       <c r="AG54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,22 +5099,23 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
       <c r="G57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
@@ -4999,7 +5130,7 @@
         <v>400</v>
       </c>
       <c r="L57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
@@ -5008,7 +5139,7 @@
         <v>300</v>
       </c>
       <c r="O57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -5020,7 +5151,7 @@
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -5041,11 +5172,11 @@
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>100</v>
-      </c>
       <c r="AB57" s="3">
         <v>100</v>
       </c>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5103,70 +5237,73 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>2700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2200</v>
       </c>
       <c r="R58" s="3">
         <v>2200</v>
       </c>
       <c r="S58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T58" s="3">
         <v>2100</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1900</v>
       </c>
       <c r="U58" s="3">
         <v>1900</v>
       </c>
       <c r="V58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W58" s="3">
         <v>1800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>500</v>
       </c>
-      <c r="AG58" s="3">
-        <v>100</v>
-      </c>
       <c r="AH58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5201,84 +5338,87 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>16500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>500</v>
       </c>
       <c r="X59" s="3">
         <v>500</v>
       </c>
       <c r="Y59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>400</v>
       </c>
       <c r="AB59" s="3">
         <v>400</v>
       </c>
       <c r="AC59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD59" s="3">
         <v>600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>500</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>200</v>
       </c>
       <c r="AH59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
       </c>
       <c r="G60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H60" s="3">
         <v>400</v>
@@ -5293,76 +5433,79 @@
         <v>400</v>
       </c>
       <c r="L60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M60" s="3">
         <v>300</v>
       </c>
       <c r="N60" s="3">
+        <v>300</v>
+      </c>
+      <c r="O60" s="3">
         <v>19500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>2800</v>
       </c>
       <c r="U60" s="3">
         <v>2800</v>
       </c>
       <c r="V60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W60" s="3">
         <v>2500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5454,13 +5597,16 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5479,14 +5625,14 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
@@ -5503,8 +5649,8 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,22 +6006,25 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
-      </c>
-      <c r="E66" s="3">
-        <v>500</v>
       </c>
       <c r="F66" s="3">
         <v>500</v>
       </c>
       <c r="G66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H66" s="3">
         <v>400</v>
@@ -5881,76 +6039,79 @@
         <v>400</v>
       </c>
       <c r="L66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M66" s="3">
         <v>300</v>
       </c>
       <c r="N66" s="3">
+        <v>300</v>
+      </c>
+      <c r="O66" s="3">
         <v>19500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>2800</v>
       </c>
       <c r="U66" s="3">
         <v>2800</v>
       </c>
       <c r="V66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W66" s="3">
         <v>2500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6271,16 +6439,19 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>200</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8000</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-7600</v>
       </c>
       <c r="S72" s="3">
         <v>-7600</v>
       </c>
       <c r="T72" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="U72" s="3">
         <v>-7100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>-4900</v>
       </c>
       <c r="AC72" s="3">
         <v>-4900</v>
       </c>
       <c r="AD72" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
       <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
         <v>-200</v>
       </c>
-      <c r="G76" s="3">
-        <v>100</v>
-      </c>
       <c r="H76" s="3">
+        <v>100</v>
+      </c>
+      <c r="I76" s="3">
         <v>300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-19100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-3600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-3300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-3400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-2700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-2400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-2100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-400</v>
       </c>
-      <c r="AF76" s="3">
-        <v>100</v>
-      </c>
       <c r="AG76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH76" s="3">
         <v>400</v>
       </c>
-      <c r="AH76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
-        <v>100</v>
-      </c>
       <c r="F81" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
         <v>-300</v>
       </c>
       <c r="H81" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I81" s="3">
         <v>-400</v>
       </c>
       <c r="J81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
-        <v>100</v>
-      </c>
       <c r="Q81" s="3">
+        <v>100</v>
+      </c>
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
-        <v>100</v>
-      </c>
       <c r="S81" s="3">
+        <v>100</v>
+      </c>
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-300</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7259,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -7271,11 +7470,11 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
-        <v>100</v>
-      </c>
       <c r="AA83" s="3">
         <v>100</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7805,7 +8022,7 @@
         <v>-100</v>
       </c>
       <c r="G89" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
@@ -7817,19 +8034,19 @@
         <v>-300</v>
       </c>
       <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
         <v>-400</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-500</v>
       </c>
       <c r="M89" s="3">
         <v>-500</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
@@ -7859,19 +8076,19 @@
         <v>-100</v>
       </c>
       <c r="Y89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-200</v>
       </c>
       <c r="AD89" s="3">
         <v>-200</v>
@@ -7883,13 +8100,16 @@
         <v>-200</v>
       </c>
       <c r="AG89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AH89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7933,11 +8154,11 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -7957,14 +8178,14 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -7986,14 +8207,14 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -8007,8 +8228,8 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
@@ -8016,14 +8237,17 @@
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8227,10 +8457,10 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -8251,17 +8481,17 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -8304,20 +8534,23 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8777,14 +9023,14 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>100</v>
-      </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
@@ -8813,37 +9059,40 @@
         <v>100</v>
       </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
-        <v>100</v>
-      </c>
       <c r="AA100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB100" s="3">
         <v>200</v>
       </c>
       <c r="AC100" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
-        <v>100</v>
-      </c>
       <c r="AE100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>200</v>
       </c>
       <c r="AG100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8949,13 +9201,13 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-300</v>
       </c>
       <c r="H102" s="3">
         <v>-300</v>
@@ -8967,17 +9219,17 @@
         <v>-300</v>
       </c>
       <c r="K102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
@@ -9015,20 +9267,20 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
         <v>0</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
     </row>
